--- a/Vulnerability Test Results/findings.xlsx
+++ b/Vulnerability Test Results/findings.xlsx
@@ -217,7 +217,7 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-23 08:37:29 UTC</t>
+    <t>2026-07-23 09:24:34 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
